--- a/reports/ai_readiness_2026-W21.xlsx
+++ b/reports/ai_readiness_2026-W21.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/ai_readiness_2026-W21.xlsx
+++ b/reports/ai_readiness_2026-W21.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/ai_readiness_2026-W21.xlsx
+++ b/reports/ai_readiness_2026-W21.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/ai_readiness_2026-W21.xlsx
+++ b/reports/ai_readiness_2026-W21.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
